--- a/artfynd/A 62951-2025 artfynd.xlsx
+++ b/artfynd/A 62951-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>130130911</v>
       </c>
       <c r="B3" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62951-2025 artfynd.xlsx
+++ b/artfynd/A 62951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130130915</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130130911</v>
       </c>
       <c r="B3" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62951-2025 artfynd.xlsx
+++ b/artfynd/A 62951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130130915</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130130911</v>
       </c>
       <c r="B3" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62951-2025 artfynd.xlsx
+++ b/artfynd/A 62951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130130915</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>130130911</v>
       </c>
       <c r="B3" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62951-2025 artfynd.xlsx
+++ b/artfynd/A 62951-2025 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>130130911</v>
       </c>
       <c r="B3" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62951-2025 artfynd.xlsx
+++ b/artfynd/A 62951-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130130915</v>
+        <v>130130911</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -709,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>mugglomE, Nb</t>
+          <t>mugglomF, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>828673</v>
+        <v>828860</v>
       </c>
       <c r="R2" t="n">
-        <v>7360511</v>
+        <v>7360413</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,14 +776,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>gammal,senvuxen</t>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # gammal,senvuxen</t>
+          <t>Horizontal, dead with ground contact # nästan barklös # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,32 +801,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130130911</v>
+        <v>130130915</v>
       </c>
       <c r="B3" t="n">
-        <v>91758</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,14 +835,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>mugglomF, Nb</t>
+          <t>mugglomE, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>828860</v>
+        <v>828673</v>
       </c>
       <c r="R3" t="n">
-        <v>7360413</v>
+        <v>7360511</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,14 +902,14 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>gammal,senvuxen</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # nästan barklös # Picea abies</t>
+          <t>Picea abies # gammal,senvuxen</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 62951-2025 artfynd.xlsx
+++ b/artfynd/A 62951-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130130911</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,8 +934,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130130915</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>